--- a/Result/checksun_type/五金元件及零配件.xlsx
+++ b/Result/checksun_type/五金元件及零配件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>351.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>316.15</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>276.55</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>316.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>276.55</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>175402.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>254939.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>254939.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1000842.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>618029.38</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>618029.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-111100.8024302281</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>175402</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>175402.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>351.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>312.27</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>274.56</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>312.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>274.56</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>220541.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>761671.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>761671.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1148734.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>615823.14</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>615823.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-70151.76124752988</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>220541</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>220541.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>353.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>307.9</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>272.55</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>272.55</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>168318.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1268670.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1268670</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1242401.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>613169.58</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>613169.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-13984.03237054916</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>168318</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>168318.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>353.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>303.82</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>270.6</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>303.82</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>270.6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>361908.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1576061.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1576061.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1339662.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>611421.82</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>611421.8199999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>72350.3314669428</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>361908</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>361908.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>349.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>300.45</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>268.82</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>300.45</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>268.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>348529.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1681953.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1681953.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1396072.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>605427.58</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>605427.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>172359.4108252549</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>348529</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>348529.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>337.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>296.12</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>266.61</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>296.12</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>266.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2709063.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1746746.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1746746</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1455654.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>599287.18</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>599287.1800000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>310507.2952362271</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2709063</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2709063.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>327.7</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>292.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>264.54</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>292.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>264.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2755532.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1535797.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1535797.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1211321.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>546222.04</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>546222.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>243857.5124220364</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2755532</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2755532.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>316.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>287.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>262.26</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>287.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>262.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1705277.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1216132.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1216132.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>964029.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>492721.26</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>492721.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>134955.5186724056</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1705277</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1705277.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>308.4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>282.5</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>260.2</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>260.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>891365.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1103263.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1103263.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>829715.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>461473.74</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>461473.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>87088.7233632044</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>891365</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>891365.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>302.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>279.4</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>259.07</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>259.07</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>672493.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1110191.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1110191.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>815668.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>450769.56</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>450769.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>102802.1328013742</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>672493</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>672493.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>301.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>277.2</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>258.37</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>258.37</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1654321.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1164563.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1164563.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>839176.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>448472.9</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>448472.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>145028.9272558534</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1654321</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1654321.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>22.78</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3388.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>3388.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2604.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2869.44</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2869.44</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>366.1223336369967</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>9458</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>22.38</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1482.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2005.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2005.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2493.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2744.18</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2744.18</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-206.215010213768</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1482</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1482.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>22.37</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>22.62</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>23.31</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1564.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1993.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1993.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2593.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2767.54</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2767.54</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-161.9035367786546</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1564</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1564.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>22.43</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>22.64</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23.37</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3759.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1965.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1965.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3319.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2794.42</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2794.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-101.6048769863974</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3759</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3759.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>23.44</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23.44</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>680.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1478.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1478.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3093.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2764.8</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2764.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-247.0137602479449</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>680</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>22.86</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>23.52</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2542.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1821.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1821.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3254.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2867.44</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2867.44</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-116.0259591841573</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2542</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2542.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>23.14</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>23.61</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>23.61</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1423.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2982.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2982</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3146.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>3156.52</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>3156.52</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-124.2567448364548</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1423</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1423.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>23.29</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23.65</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1425.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3193.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3193.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>3280.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>3195.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>3195.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-11.68441202414942</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1425</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1425.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>23.36</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>23.68</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1322.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>4673.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>4673.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3200.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>3233.78</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>3233.78</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>149.3362209942916</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1322</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1322.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>23.02</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>22.78</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>23.72</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23.72</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2394.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>4708.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>4708.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3208.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>3272.1</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>3272.1</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>385.0679745565544</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2394</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2394.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>22.72</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>23.77</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>23.77</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>8346.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>4688.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>4688.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3120.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>3253.26</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>3253.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>593.2180519827671</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>8346</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>8346.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>14.28</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>14.88</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>16.09</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2109.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1826.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1826.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>3087.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3994.46</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3994.46</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-416.1291410816912</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2109</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2109.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>14.17</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>16.15</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>16.15</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1442.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1958.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1958.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3242.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>4217.06</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>4217.06</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-427.5095529198452</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1442</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1442.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>14.19</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>16.23</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>16.23</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1550.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>2490.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>2490.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3518.4</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>4258.64</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>4258.64</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-357.034800084356</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1550</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1550.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>14.32</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>16.31</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>16.31</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>2432.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>3483.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>3483.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3662.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>4294.64</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>4294.64</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-255.1767674592165</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>2432</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>2432.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>14.51</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>15.18</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>16.39</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1600.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>3719.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>3719.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3898.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>4371.26</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>4371.26</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-195.0518362997591</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1600</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>14.65</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>16.47</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>16.47</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2768.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>4349.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>4349.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>4053.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>4446.48</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>4446.48</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-13.05008334697095</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2768</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2768.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>16.55</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>4102.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4526.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4526.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>4166.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>4488.46</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>4488.46</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>122.2756381336894</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>4102</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>4102.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>15.47</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>16.63</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>16.63</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>6515.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4546.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4546.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>4170.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>4500.94</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>4500.94</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>168.302538887001</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>6515</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>6515.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>16.71</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>16.71</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>3612.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3841.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3841.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3829.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>4467.94</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>4467.94</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-30.49126499708973</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>3612</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>3612.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>16.78</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>16.78</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>4749.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>4077.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>4077.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>3684.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>4569.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>4569.74</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2.357725367323383</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>4749</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>4749.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>16.86</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3655.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3758.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3758</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>3694.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>4706.84</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>4706.84</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-83.90417856168142</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3655</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3655.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>16.59</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>16.88</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>18.16</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>18.16</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>204.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>208.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>208.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>259.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>340.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>340.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-48.4001672152865</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>204</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>16.5</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>16.94</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>18.21</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>18.21</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>155.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>267.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>267.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>267.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>346.26</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>346.26</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-50.62395308068739</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>155</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>16.57</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>18.27</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>18.27</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>33.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>293.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>293.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>276.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>360.38</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>360.38</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-46.7427917069499</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>33</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>18.34</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>18.34</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>165.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>325.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>325.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>341.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>374.88</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>374.88</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-26.45746146921948</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>165</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>16.83</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>17.27</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>18.41</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>486.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>342.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>342.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>373.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>424.1</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>424.1</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-10.67636607713251</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>486</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>486.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>16.99</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>18.49</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>498.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>311.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>311.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>364.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>467.08</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>467.08</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-22.14350244282491</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>498</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>498.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>17.12</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>18.56</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>18.56</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>284.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>266.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>266.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>332.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>665.16</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>665.16</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-39.02000073514182</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>284</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>284.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>17.13</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>18.65</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>194.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>259.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>259</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>364.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>784.06</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>784.0599999999999</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-38.80714112648229</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>194</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>194.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>17.01</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>18.69</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>251.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>358.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>358.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>545.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>880.72</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>880.72</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-27.47422950245146</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>251</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>251.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>16.91</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>18.69</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>329.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>403.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>403.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>560.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>891.2</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>891.2</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-16.41027612874842</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>329</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>329.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>16.79</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>17.87</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>18.69</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>275.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>417.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>417.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>587.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>889.62</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>889.62</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-8.375690018860155</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>275</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>40.14</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>40.34</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>40.88</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>40.88</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1008.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>58.77026642390729</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1008</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1008.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>40.35</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>40.93</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2.954113860118895</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>159</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>40.21</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>40.99</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>40.99</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>0</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>1.17967744797707</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>0</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>40.18</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>40.44</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>41.02</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>145.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>208.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>208.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>198.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>0</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>1.17967744797707</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>145</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>40.08</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>40.48</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>41.04</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>41.04</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>195.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>215.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>215.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>192.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>0</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>7.197985201104501</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>195</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>39.76</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>40.42</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>41.02</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>508.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>176.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>176.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>197.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>0</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>10.18135394838995</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>508</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>508.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>39.71</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>156.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>118.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>118.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>162.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>0</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-19.4560247679305</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>156</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>39.91</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>40.52</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>41.1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>164</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>0</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-23.38599347810501</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>40</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>40.61</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>178.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>188.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>188.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>0</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-15.73644901127915</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>178</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>40.60000000000001</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>40.73</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>169.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>169.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-19.03222659398224</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>40.68000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>40.82</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>41.19</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>41.19</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>217.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>217.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>217.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>0</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-4.203615048058737</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>217</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>193.6</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>199.42</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>206.37</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>206.37</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>103692746.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>118689542.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>118689542.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>168956434.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>210639255.6</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>210639255.6</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-21994999.89875582</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>103692746</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>103692746.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>192.8</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>199.6</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>206.79</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>206.79</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>83296686.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>132951227.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>132951227.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>187104254.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>216056658.14</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>216056658.14</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-21153128.92795646</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>83296686</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>83296686.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>190.5</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>199.9</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>207.4</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>207.4</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>61949648.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>158673800.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>158673800.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>190641450.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>221503976.62</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>221503976.62</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-17009695.07938755</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>61949648</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>61949648.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>191.3</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>200.98</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>208.27</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>208.27</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>171049391.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>185721656.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>185721656</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>194467502.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>225715579.68</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>225715579.68</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-8195832.11431092</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>171049391</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>171049391.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>193.8</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>202.12</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>209.21</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>202.12</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>209.21</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>173459243.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>214560702.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>214560702.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>190367255.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>229384096.36</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>229384096.36</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-7001149.195833266</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>173459243</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>173459243.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>197.3</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>203.28</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>209.98</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>203.28</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>209.98</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>175001170.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>219223326.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>219223326.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>198890553.9</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>237319445.14</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>237319445.14</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-5302616.698156834</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>175001170</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>175001170.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>200.4</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>204.9</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>210.68</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>210.68</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>211909550.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>241257280.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>241257280.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>195768003.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>243255926.66</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>243255926.66</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-2851968.997970581</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>211909550</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>211909550.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>203.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>206.82</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>211.51</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>206.82</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>211.51</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>197188926.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>222609099.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>222609099.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>192571153.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>247917131.98</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>247917131.98</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-3203656.962062716</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>197188926</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>197188926.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>205.3</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>208.1</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>212.12</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>208.1</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>212.12</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>315244622.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>203213349.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>203213349.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>184850244.1</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>256109616.18</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>256109616.18</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-2014442.304977804</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>315244622</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>315244622.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>209.5</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>212.87</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>212.87</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>196772364.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>166173809.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>166173809</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>176703005.8</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>270755220.04</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>270755220.04</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-12892444.42682159</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>196772364</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>196772364.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>204.9</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>209.5</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>213.68</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>213.68</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>285170940.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>178557781.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>178557781.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>186036429.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>275437421.42</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>275437421.42</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-15278546.79992619</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>285170940</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>285170940.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>48.27</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>52.89</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>58.67</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>58.67</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>533.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>4716.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>4716.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>3793.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>5834.36</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>5834.36</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-842.1280039432459</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>533</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>533.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>47.73999999999999</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>53.57</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>58.94</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>58.94</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1493.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>4966.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>4966</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>3996.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>6021.16</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>6021.16</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-597.790131482544</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1493</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1493.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>47.51</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>54.26</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>1172.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>5624.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>5624.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>4371.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>6064.78</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>6064.78</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-330.2435232714515</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>1172</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>1172.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>47.91</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>55.07</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>59.64</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>59.64</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>18036.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5852.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>5852.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>4334.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>6105.66</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>6105.66</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>98.15318571837724</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>18036</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>18036.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>48.7</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>55.87</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>60.04</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>60.04</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>2348.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>2553.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>2553.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3005.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>5804.76</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>5804.76</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-1100.214129500383</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>2348</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>2348.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>49.23</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>60.42</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>60.42</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1781.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>2869.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>2869.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>4065.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>5830.72</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>5830.72</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-1092.016932330739</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1781</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1781.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>50.13</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>60.8</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>4785.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>3026.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>3026.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>6040.2</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>5817.18</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>5817.18</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-980.5560459337212</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>4785</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>4785.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>51.06</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>57.87</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>61.17</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>61.17</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>2314.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>3119.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>3119.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>6480.8</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>5796.92</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>5796.92</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-1108.163492297492</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2314</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2314.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>51.72000000000001</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>58.33</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>61.48</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>61.48</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>1540.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2816.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2816.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>8089.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>5943.54</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>5943.54</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-986.1325766636837</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>1540</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>1540.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>52.38</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>58.74</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>61.78</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>61.78</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>3928.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>3456.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>3456.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>9910.5</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>6081.78</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>6081.78</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-693.6551051631113</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>3928</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>3928.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>53.66</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>62.13</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>62.13</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>2567.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>5261.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>5261.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>11365.7</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6269.82</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6269.82</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-506.913892120755</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>2567</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>2567.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>46.26000000000001</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>49.64</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>51.43</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>51.43</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>5529.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>11106.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>11106.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>17860.4</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>25078.5</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>25078.5</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-2059.479234116441</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>5529</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>5529.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>46.8</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>51.51</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>51.51</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>17904.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>11727.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>11727</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>20373.0</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>25219.4</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>25219.4</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-1418.060458855532</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>17904</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>17904.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>47.84</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>50.14</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>51.63</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>51.63</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>12188.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>13275.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>13275.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>21118.4</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>25145.6</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>25145.6</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-1776.995763523681</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>12188</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>12188.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>48.77</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>50.36</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>51.7</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>10904.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>12471.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>12471.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>21537.7</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>25036.26</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>25036.26</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-1613.867778638047</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>10904</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>10904.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>49.7</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>50.54</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>51.74</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>51.74</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>9009.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>14303.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>14303.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>22685.8</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>25014.46</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>25014.46</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-1185.618236707211</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>9009</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>9009.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>50.76000000000001</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>50.66</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>51.75</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>51.75</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>8630.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>24614.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>24614</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>23039.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>25018.82</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>25018.82</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-328.4539540664737</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>8630</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>8630.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>51.75</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>51.75</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>25646.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>29019.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>29019</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>25297.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>24993.48</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>24993.48</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>948.4040909226678</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>25646</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>25646.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>50.86</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>51.72</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>51.72</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>8167.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>28961.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>28961.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>26806.2</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>24583.08</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>24583.08</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>915.4725805170638</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>8167</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>8167.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>51.04</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>51.69</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>51.69</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>20064.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>30604.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>30604.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>26267.7</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>24514.12</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>24514.12</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>2708.482116347728</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>20064</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>20064.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>50.8</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>51.63</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>51.63</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>60563.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>31068.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>31068.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>24854.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>24215.78</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>24215.78</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>3898.514234807692</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>60563</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>60563.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>50.36</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>50.79</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>51.52</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>51.52</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>30655.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>21465.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>21465.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>19324.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>23060.82</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>23060.82</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>1120.148895650218</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>30655</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>30655.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>308.6</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>308.12</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>320.64</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>320.64</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>1103751756.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>539114722.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>539114722</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>535884533.1</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>995590959.64</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>995590959.64</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-3821590.401730537</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>1103751756</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>1103751756.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>304.3</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>307.68</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>320.85</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>307.68</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>320.85</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>302687135.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>383463729.6</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>383463729.6</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>456635015.3</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>1001483363.76</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>1001483363.76</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-61492460.2597667</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>302687135</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>302687135.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>302.0</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>307.85</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>321.35</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>307.85</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>321.35</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>375263982.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>441496073.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>441496073.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>485774035.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>1010779691.04</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>1010779691.04</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-55854905.65482664</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>375263982</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>375263982.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>303.4</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>308.32</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>321.9</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>308.32</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>321.9</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>464055602.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>509792590.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>509792590.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>470990914.2</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>1029457781.74</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>1029457781.74</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-53582528.910097</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>464055602</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>464055602.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>306.2</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>309.27</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>322.8</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>309.27</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>322.8</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>449815135.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>529731892.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>529731892.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>501540444.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>1045686232.46</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>1045686232.46</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-57936002.52797961</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>449815135</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>449815135.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>305.8</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>309.77</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>323.4</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>309.77</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>323.4</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>325496794.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>532654344.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>532654344.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>506007519.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>1052426061.88</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>1052426061.88</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-60560343.28466988</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>325496794</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>325496794.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>308.5</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>310.98</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>324.21</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>310.98</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>324.21</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>592848855.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>529806301.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>529806301</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>523707025.7</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>1067937693.2</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>1067937693.2</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-48826709.85548925</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>592848855</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>592848855.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>311.2</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>312.25</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>324.94</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>312.25</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>324.94</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>716746568.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>530051997.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>530051997</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>516053870.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>1076800093.92</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>1076800093.92</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-58965428.99753511</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>716746568</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>716746568.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>309.6</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>313.0</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>325.27</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>325.27</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>563752109.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>432189237.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>432189237.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>476257879.9</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>1109149349.46</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>1109149349.46</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-84618160.27197444</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>563752109</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>563752109.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>307.3</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>314.5</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>325.87</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>325.87</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>464427395.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>473348997.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>473348997.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>475813386.8</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>1128378027.98</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>1128378027.98</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-101850578.6186029</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>464427395</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>464427395.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>307.7</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>315.8</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>326.69</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>326.69</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>311256578.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>479360693.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>479360693.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>486640404.1</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>1143137996.64</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>1143137996.64</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-112188864.8059791</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>311256578</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>311256578.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>123.3</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>122.42</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>125.14</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>122.42</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>125.14</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>11609428.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>6719481.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>6719481.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>7150527.2</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>15293526.28</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>15293526.28</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-965363.1883415803</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>11609428</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>11609428.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>122.4</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>125.18</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>125.18</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>4633040.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>5991848.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>5991848.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>7634003.7</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>16065792.0</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>16065792</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-1483148.170541969</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>4633040</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>4633040.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>122.22</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>125.29</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>122.22</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>125.29</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>8641493.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>7000850.6</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>7000850.6</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>8614756.9</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>16825468.54</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>16825468.54</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-1422401.281880314</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>8641493</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>8641493.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>121.7</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>122.28</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>125.42</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>125.42</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>4734929.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>6604752.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>6604752.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>9054730.6</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>17609341.86</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>17609341.86</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-1714297.07372508</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>4734929</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>4734929.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>122.4</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>125.59</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>125.59</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>3978518.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>6594184.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>6594184.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>9317338.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>17881187.08</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>17881187.08</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-1651505.738013135</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>3978518</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>3978518.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>122.5</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>122.58</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>125.79</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>122.58</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>125.79</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>7971262.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>7581572.8</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>7581572.8</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>9345173.1</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>17977443.94</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>17977443.94</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-1421777.446352744</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>7971262</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>7971262.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>122.8</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>122.72</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>125.97</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>125.97</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>9678051.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>9276159.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>9276159</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>9696127.1</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>18004600.42</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>18004600.42</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-1470610.406611016</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>9678051</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>9678051.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>122.7</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>122.88</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>126.14</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>122.88</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>126.14</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>6661002.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>10228663.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>10228663.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>9419381.8</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>18121182.54</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>18121182.54</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-1670720.22817244</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>6661002</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>6661002.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>122.5</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>123.08</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>126.29</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>123.08</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>126.29</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>4682090.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>11504708.8</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>11504708.8</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>9279362.6</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>18380431.58</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>18380431.58</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-1573667.572254034</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>4682090</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>4682090.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>122.2</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>123.18</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>126.41</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>123.18</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>126.41</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>8915459.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>12040493.2</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>12040493.2</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>11577402.5</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>18861599.42</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>18861599.42</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-1166792.221932948</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>8915459</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>8915459.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>121.9</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>123.02</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>126.54</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>126.54</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>16444193.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>11108773.4</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>11108773.4</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>11725684.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>18989989.28</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>18989989.28</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-997445.8206909355</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>16444193</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>16444193.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
